--- a/samples/incoming_inspection/수입검사_대성정공.xlsx
+++ b/samples/incoming_inspection/수입검사_대성정공.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -57,7 +54,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -424,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -439,77 +436,105 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>품번</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>품명</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>로트번호</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>협력사</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>검사일</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>입고수량</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>검사수량</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>불량수량</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>품번</t>
+          <t>HB-6300</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>스프링 와셔</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>로트번호</t>
+          <t>DS260901-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>협력사</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>검사일</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>입고수량</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>검사수량</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>불량수량</t>
-        </is>
+          <t>대성정공</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>불합격</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HB-6300</t>
+          <t>HB-1001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스프링 와셔</t>
+          <t>브라켓 A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DS260901-01</t>
+          <t>DS260901-02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -521,34 +546,34 @@
         <v>46266</v>
       </c>
       <c r="F3" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>불합격</t>
+          <t>합격</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HB-1001</t>
+          <t>HB-3101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>브라켓 A</t>
+          <t>하우징 베이스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DS260901-02</t>
+          <t>DS260901-03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -560,17 +585,17 @@
         <v>46266</v>
       </c>
       <c r="F4" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>합격</t>
+          <t>불합격</t>
         </is>
       </c>
     </row>
@@ -587,7 +612,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DS260901-03</t>
+          <t>DS260902-04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -596,37 +621,32 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F5" t="n">
         <v>1000</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>불합격</t>
+          <t>합격</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HB-3101</t>
+          <t>HB-1001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>하우징 베이스</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DS260902-04</t>
+          <t>브라켓 A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -638,29 +658,34 @@
         <v>46267</v>
       </c>
       <c r="F6" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>합격</t>
+          <t>불합격</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HB-1001</t>
+          <t>HB-5201</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>브라켓 A</t>
+          <t>너트 M6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DS260902-06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -672,34 +697,34 @@
         <v>46267</v>
       </c>
       <c r="F7" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>불합격</t>
+          <t>합격</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HB-5201</t>
+          <t>HB-2011</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>너트 M6</t>
+          <t>샤프트 25mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DS260902-06</t>
+          <t>DS260903-07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -708,10 +733,10 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F8" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="G8" t="n">
         <v>13</v>
@@ -728,17 +753,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HB-2011</t>
+          <t>HB-4006</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>샤프트 25mm</t>
+          <t>O링 30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DS260903-07</t>
+          <t>DS260903-08</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -749,11 +774,13 @@
       <c r="E9" s="2" t="n">
         <v>46268</v>
       </c>
-      <c r="F9" t="n">
-        <v>300</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>12개</t>
+        </is>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -767,17 +794,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HB-4006</t>
+          <t>HB-2010</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>O링 30</t>
+          <t>샤프트 20mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DS260903-08</t>
+          <t>DS260903-09</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -788,13 +815,11 @@
       <c r="E10" s="2" t="n">
         <v>46268</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>12개</t>
-        </is>
+      <c r="F10" t="n">
+        <v>1000</v>
       </c>
       <c r="G10" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -808,17 +833,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HB-2010</t>
+          <t>HB-2011</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>샤프트 20mm</t>
+          <t>샤프트 25mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DS260903-09</t>
+          <t>DS260904-10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -827,10 +852,10 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -847,17 +872,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HB-2011</t>
+          <t>HB-7010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>샤프트 25mm</t>
+          <t>커넥터 4P</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DS260904-10</t>
+          <t>DS260904-11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -869,13 +894,13 @@
         <v>46269</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G12" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -886,17 +911,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HB-7010</t>
+          <t>HB-1001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>커넥터 4P</t>
+          <t>브라켓 A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DS260904-11</t>
+          <t>DS260904-12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -908,34 +933,34 @@
         <v>46269</v>
       </c>
       <c r="F13" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
         <v>32</v>
       </c>
       <c r="H13" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>합격</t>
+          <t>불합격</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HB-1001</t>
+          <t>HB-5201</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>브라켓 A</t>
+          <t>너트 M6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DS260904-12</t>
+          <t>DS260905-13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -944,37 +969,37 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>불합격</t>
+          <t xml:space="preserve">합격 </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HB-5201</t>
+          <t>HB-2011</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>너트 M6</t>
+          <t>샤프트 25mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DS260905-13</t>
+          <t>DS260905-14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -989,31 +1014,31 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">합격 </t>
+          <t>불합격</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HB-2011</t>
+          <t>HB-7010</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>샤프트 25mm</t>
+          <t>커넥터 4P</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DS260905-14</t>
+          <t>DS260905-15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1025,54 +1050,15 @@
         <v>46270</v>
       </c>
       <c r="F16" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>불합격</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>HB-7010</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>커넥터 4P</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DS260905-15</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>대성정공</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>46270</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G17" t="n">
-        <v>50</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
         <is>
           <t>합격</t>
         </is>
